--- a/sample_imports/Template_HocKy.xlsx
+++ b/sample_imports/Template_HocKy.xlsx
@@ -41,7 +41,7 @@
     <t>HK2425_1</t>
   </si>
   <si>
-    <t>Học kỳ 1 (2024-2025)</t>
+    <t>Học kỳ 1</t>
   </si>
   <si>
     <t>2024-2025</t>
@@ -59,7 +59,7 @@
     <t>HK2425_2</t>
   </si>
   <si>
-    <t>Học kỳ 2 (2024-2025)</t>
+    <t>Học kỳ 2</t>
   </si>
   <si>
     <t>2025-01-20</t>
@@ -486,18 +486,23 @@
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="11.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="24.708" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="11.711" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="16.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="11.569" customWidth="true" style="0"/>
+    <col min="2" max="2" width="24.708" customWidth="true" style="0"/>
+    <col min="3" max="3" width="11.711" customWidth="true" style="0"/>
+    <col min="4" max="4" width="15.139" customWidth="true" style="0"/>
+    <col min="5" max="5" width="16.282" customWidth="true" style="0"/>
+    <col min="6" max="6" width="13.997" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" customHeight="1" ht="28">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1"/>
+      <c r="C1"/>
+      <c r="D1"/>
+      <c r="E1"/>
+      <c r="F1"/>
     </row>
     <row r="2" spans="1:6" customHeight="1" ht="24">
       <c r="A2" s="2" t="s">
